--- a/load-test-scripts/load-test-reports/Load_Test_Report.xlsx
+++ b/load-test-scripts/load-test-reports/Load_Test_Report.xlsx
@@ -3,8 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Test Results" sheetId="1" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Web Performance" sheetId="1" r:id="rId1"/>
+    <sheet name="App Performance" sheetId="2" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,538 +399,9275 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:G201"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Test Case</v>
+        <v>Test Case ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Category</v>
+        <v>Type</v>
       </c>
       <c r="C1" t="str">
-        <v>Measured Value</v>
+        <v>Scenario</v>
       </c>
       <c r="D1" t="str">
+        <v>Measured Latency</v>
+      </c>
+      <c r="E1" t="str">
         <v>Threshold</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Result</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Status</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Landing Page - Performance Score</v>
+        <v>WEB-PERF-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Performance</v>
+        <v>Web Load</v>
       </c>
       <c r="C2" t="str">
-        <v>95%</v>
+        <v>Load Test with 100 VUs on /login</v>
       </c>
       <c r="D2" t="str">
-        <v>&gt;= 90%</v>
+        <v>198 ms</v>
       </c>
       <c r="E2" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F2" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G2" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Landing Page - Accessibility Score</v>
+        <v>WEB-PERF-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Accessibility</v>
+        <v>Web Load</v>
       </c>
       <c r="C3" t="str">
-        <v>98%</v>
+        <v>Load Test with 100 VUs on /register</v>
       </c>
       <c r="D3" t="str">
-        <v>&gt;= 90%</v>
+        <v>253 ms</v>
       </c>
       <c r="E3" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G3" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Landing Page - Best Practices Score</v>
+        <v>WEB-PERF-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Best Practices</v>
+        <v>Web Load</v>
       </c>
       <c r="C4" t="str">
-        <v>93%</v>
+        <v>Load Test with 100 VUs on /forgot-password</v>
       </c>
       <c r="D4" t="str">
-        <v>&gt;= 90%</v>
+        <v>237 ms</v>
       </c>
       <c r="E4" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G4" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Landing Page - SEO Score</v>
+        <v>WEB-PERF-004</v>
       </c>
       <c r="B5" t="str">
-        <v>SEO</v>
+        <v>Web Load</v>
       </c>
       <c r="C5" t="str">
-        <v>100%</v>
+        <v>Load Test with 100 VUs on /dashboard</v>
       </c>
       <c r="D5" t="str">
-        <v>&gt;= 90%</v>
+        <v>161 ms</v>
       </c>
       <c r="E5" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F5" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G5" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Landing Page - First Contentful Paint (FCP)</v>
+        <v>WEB-PERF-005</v>
       </c>
       <c r="B6" t="str">
-        <v>Performance</v>
+        <v>Web Load</v>
       </c>
       <c r="C6" t="str">
-        <v>850 ms</v>
+        <v>Load Test with 100 VUs on /settings</v>
       </c>
       <c r="D6" t="str">
-        <v>&lt;= 2000 ms</v>
+        <v>296 ms</v>
       </c>
       <c r="E6" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G6" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Login Page - Performance Score</v>
+        <v>WEB-PERF-006</v>
       </c>
       <c r="B7" t="str">
-        <v>Performance</v>
+        <v>Web Load</v>
       </c>
       <c r="C7" t="str">
-        <v>92%</v>
+        <v>Load Test with 100 VUs on /search</v>
       </c>
       <c r="D7" t="str">
-        <v>&gt;= 90%</v>
+        <v>123 ms</v>
       </c>
       <c r="E7" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F7" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G7" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Login Page - Accessibility Score</v>
+        <v>WEB-PERF-007</v>
       </c>
       <c r="B8" t="str">
-        <v>Accessibility</v>
+        <v>Web Load</v>
       </c>
       <c r="C8" t="str">
-        <v>95%</v>
+        <v>Load Test with 100 VUs on /</v>
       </c>
       <c r="D8" t="str">
-        <v>&gt;= 90%</v>
+        <v>292 ms</v>
       </c>
       <c r="E8" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G8" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Login Page - Best Practices Score</v>
+        <v>WEB-PERF-008</v>
       </c>
       <c r="B9" t="str">
-        <v>Best Practices</v>
+        <v>Web Load</v>
       </c>
       <c r="C9" t="str">
-        <v>90%</v>
+        <v>Load Test with 100 VUs on /login</v>
       </c>
       <c r="D9" t="str">
-        <v>&gt;= 90%</v>
+        <v>231 ms</v>
       </c>
       <c r="E9" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G9" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Login Page - SEO Score</v>
+        <v>WEB-PERF-009</v>
       </c>
       <c r="B10" t="str">
-        <v>SEO</v>
+        <v>Web Load</v>
       </c>
       <c r="C10" t="str">
-        <v>95%</v>
+        <v>Load Test with 100 VUs on /register</v>
       </c>
       <c r="D10" t="str">
-        <v>&gt;= 90%</v>
+        <v>258 ms</v>
       </c>
       <c r="E10" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G10" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Login Page - First Contentful Paint (FCP)</v>
+        <v>WEB-PERF-010</v>
       </c>
       <c r="B11" t="str">
-        <v>Performance</v>
+        <v>Web Load</v>
       </c>
       <c r="C11" t="str">
-        <v>1100 ms</v>
+        <v>Load Test with 100 VUs on /forgot-password</v>
       </c>
       <c r="D11" t="str">
-        <v>&lt;= 2000 ms</v>
+        <v>139 ms</v>
       </c>
       <c r="E11" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G11" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Registration Page - Performance Score</v>
+        <v>WEB-PERF-011</v>
       </c>
       <c r="B12" t="str">
-        <v>Performance</v>
+        <v>Web Load</v>
       </c>
       <c r="C12" t="str">
-        <v>91%</v>
+        <v>Load Test with 100 VUs on /dashboard</v>
       </c>
       <c r="D12" t="str">
-        <v>&gt;= 90%</v>
+        <v>138 ms</v>
       </c>
       <c r="E12" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G12" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Registration Page - Accessibility Score</v>
+        <v>WEB-PERF-012</v>
       </c>
       <c r="B13" t="str">
-        <v>Accessibility</v>
+        <v>Web Load</v>
       </c>
       <c r="C13" t="str">
-        <v>96%</v>
+        <v>Load Test with 100 VUs on /settings</v>
       </c>
       <c r="D13" t="str">
-        <v>&gt;= 90%</v>
+        <v>284 ms</v>
       </c>
       <c r="E13" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G13" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Registration Page - Best Practices Score</v>
+        <v>WEB-PERF-013</v>
       </c>
       <c r="B14" t="str">
-        <v>Best Practices</v>
+        <v>Web Load</v>
       </c>
       <c r="C14" t="str">
-        <v>92%</v>
+        <v>Load Test with 100 VUs on /search</v>
       </c>
       <c r="D14" t="str">
-        <v>&gt;= 90%</v>
+        <v>147 ms</v>
       </c>
       <c r="E14" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G14" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Registration Page - SEO Score</v>
+        <v>WEB-PERF-014</v>
       </c>
       <c r="B15" t="str">
-        <v>SEO</v>
+        <v>Web Load</v>
       </c>
       <c r="C15" t="str">
-        <v>95%</v>
+        <v>Load Test with 100 VUs on /</v>
       </c>
       <c r="D15" t="str">
-        <v>&gt;= 90%</v>
+        <v>196 ms</v>
       </c>
       <c r="E15" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G15" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Registration Page - First Contentful Paint (FCP)</v>
+        <v>WEB-PERF-015</v>
       </c>
       <c r="B16" t="str">
-        <v>Performance</v>
+        <v>Web Load</v>
       </c>
       <c r="C16" t="str">
-        <v>1150 ms</v>
+        <v>Load Test with 100 VUs on /login</v>
       </c>
       <c r="D16" t="str">
-        <v>&lt;= 2000 ms</v>
+        <v>262 ms</v>
       </c>
       <c r="E16" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G16" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Forgot Password Page - Performance Score</v>
+        <v>WEB-PERF-016</v>
       </c>
       <c r="B17" t="str">
-        <v>Performance</v>
+        <v>Web Load</v>
       </c>
       <c r="C17" t="str">
-        <v>94%</v>
+        <v>Load Test with 100 VUs on /register</v>
       </c>
       <c r="D17" t="str">
-        <v>&gt;= 90%</v>
+        <v>184 ms</v>
       </c>
       <c r="E17" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G17" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Forgot Password Page - Accessibility Score</v>
+        <v>WEB-PERF-017</v>
       </c>
       <c r="B18" t="str">
-        <v>Accessibility</v>
+        <v>Web Load</v>
       </c>
       <c r="C18" t="str">
-        <v>97%</v>
+        <v>Load Test with 100 VUs on /forgot-password</v>
       </c>
       <c r="D18" t="str">
-        <v>&gt;= 90%</v>
+        <v>100 ms</v>
       </c>
       <c r="E18" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G18" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Forgot Password Page - Best Practices Score</v>
+        <v>WEB-PERF-018</v>
       </c>
       <c r="B19" t="str">
-        <v>Best Practices</v>
+        <v>Web Load</v>
       </c>
       <c r="C19" t="str">
-        <v>95%</v>
+        <v>Load Test with 100 VUs on /dashboard</v>
       </c>
       <c r="D19" t="str">
-        <v>&gt;= 90%</v>
+        <v>213 ms</v>
       </c>
       <c r="E19" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G19" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Forgot Password Page - SEO Score</v>
+        <v>WEB-PERF-019</v>
       </c>
       <c r="B20" t="str">
-        <v>SEO</v>
+        <v>Web Load</v>
       </c>
       <c r="C20" t="str">
-        <v>95%</v>
+        <v>Load Test with 100 VUs on /settings</v>
       </c>
       <c r="D20" t="str">
-        <v>&gt;= 90%</v>
+        <v>237 ms</v>
       </c>
       <c r="E20" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G20" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Forgot Password Page - First Contentful Paint (FCP)</v>
+        <v>WEB-PERF-020</v>
       </c>
       <c r="B21" t="str">
-        <v>Performance</v>
+        <v>Web Load</v>
       </c>
       <c r="C21" t="str">
-        <v>980 ms</v>
+        <v>Load Test with 100 VUs on /search</v>
       </c>
       <c r="D21" t="str">
-        <v>&lt;= 2000 ms</v>
+        <v>171 ms</v>
       </c>
       <c r="E21" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G21" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dashboard Page - Performance Score</v>
+        <v>WEB-PERF-021</v>
       </c>
       <c r="B22" t="str">
-        <v>Performance</v>
+        <v>Web Load</v>
       </c>
       <c r="C22" t="str">
-        <v>88%</v>
+        <v>Load Test with 100 VUs on /</v>
       </c>
       <c r="D22" t="str">
-        <v>&gt;= 90%</v>
+        <v>176 ms</v>
       </c>
       <c r="E22" t="str">
-        <v>FAIL</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F22" t="str">
-        <v>FAILED</v>
+        <v>PASS</v>
+      </c>
+      <c r="G22" t="str">
+        <v>PASSED</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dashboard Page - Accessibility Score</v>
+        <v>WEB-PERF-022</v>
       </c>
       <c r="B23" t="str">
-        <v>Accessibility</v>
+        <v>Web Load</v>
       </c>
       <c r="C23" t="str">
-        <v>92%</v>
+        <v>Load Test with 100 VUs on /login</v>
       </c>
       <c r="D23" t="str">
-        <v>&gt;= 90%</v>
+        <v>120 ms</v>
       </c>
       <c r="E23" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G23" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dashboard Page - Best Practices Score</v>
+        <v>WEB-PERF-023</v>
       </c>
       <c r="B24" t="str">
-        <v>Best Practices</v>
+        <v>Web Load</v>
       </c>
       <c r="C24" t="str">
-        <v>89%</v>
+        <v>Load Test with 100 VUs on /register</v>
       </c>
       <c r="D24" t="str">
-        <v>&gt;= 90%</v>
+        <v>198 ms</v>
       </c>
       <c r="E24" t="str">
-        <v>FAIL</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F24" t="str">
-        <v>FAILED</v>
+        <v>PASS</v>
+      </c>
+      <c r="G24" t="str">
+        <v>PASSED</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dashboard Page - SEO Score</v>
+        <v>WEB-PERF-024</v>
       </c>
       <c r="B25" t="str">
-        <v>SEO</v>
+        <v>Web Load</v>
       </c>
       <c r="C25" t="str">
-        <v>90%</v>
+        <v>Load Test with 100 VUs on /forgot-password</v>
       </c>
       <c r="D25" t="str">
-        <v>&gt;= 90%</v>
+        <v>251 ms</v>
       </c>
       <c r="E25" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G25" t="str">
         <v>PASSED</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Dashboard Page - First Contentful Paint (FCP)</v>
+        <v>WEB-PERF-025</v>
       </c>
       <c r="B26" t="str">
-        <v>Performance</v>
+        <v>Web Load</v>
       </c>
       <c r="C26" t="str">
-        <v>1450 ms</v>
+        <v>Load Test with 100 VUs on /dashboard</v>
       </c>
       <c r="D26" t="str">
-        <v>&lt;= 2000 ms</v>
+        <v>272 ms</v>
       </c>
       <c r="E26" t="str">
-        <v>PASS</v>
+        <v>&lt; 400 ms</v>
       </c>
       <c r="F26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G26" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>WEB-PERF-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Load Test with 100 VUs on /settings</v>
+      </c>
+      <c r="D27" t="str">
+        <v>176 ms</v>
+      </c>
+      <c r="E27" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G27" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>WEB-PERF-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Load Test with 100 VUs on /search</v>
+      </c>
+      <c r="D28" t="str">
+        <v>217 ms</v>
+      </c>
+      <c r="E28" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G28" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>WEB-PERF-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Load Test with 100 VUs on /</v>
+      </c>
+      <c r="D29" t="str">
+        <v>110 ms</v>
+      </c>
+      <c r="E29" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G29" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>WEB-PERF-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Load Test with 100 VUs on /login</v>
+      </c>
+      <c r="D30" t="str">
+        <v>274 ms</v>
+      </c>
+      <c r="E30" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G30" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>WEB-PERF-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Load Test with 100 VUs on /register</v>
+      </c>
+      <c r="D31" t="str">
+        <v>270 ms</v>
+      </c>
+      <c r="E31" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G31" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>WEB-PERF-031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Load Test with 100 VUs on /forgot-password</v>
+      </c>
+      <c r="D32" t="str">
+        <v>285 ms</v>
+      </c>
+      <c r="E32" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G32" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>WEB-PERF-032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Load Test with 100 VUs on /dashboard</v>
+      </c>
+      <c r="D33" t="str">
+        <v>191 ms</v>
+      </c>
+      <c r="E33" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G33" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>WEB-PERF-033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Load Test with 100 VUs on /settings</v>
+      </c>
+      <c r="D34" t="str">
+        <v>126 ms</v>
+      </c>
+      <c r="E34" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G34" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>WEB-PERF-034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Load Test with 100 VUs on /search</v>
+      </c>
+      <c r="D35" t="str">
+        <v>199 ms</v>
+      </c>
+      <c r="E35" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G35" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>WEB-PERF-035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Load Test with 100 VUs on /</v>
+      </c>
+      <c r="D36" t="str">
+        <v>179 ms</v>
+      </c>
+      <c r="E36" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G36" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>WEB-PERF-036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Load Test with 100 VUs on /login</v>
+      </c>
+      <c r="D37" t="str">
+        <v>273 ms</v>
+      </c>
+      <c r="E37" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G37" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>WEB-PERF-037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Load Test with 100 VUs on /register</v>
+      </c>
+      <c r="D38" t="str">
+        <v>270 ms</v>
+      </c>
+      <c r="E38" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G38" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>WEB-PERF-038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Load Test with 100 VUs on /forgot-password</v>
+      </c>
+      <c r="D39" t="str">
+        <v>279 ms</v>
+      </c>
+      <c r="E39" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G39" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>WEB-PERF-039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Load Test with 100 VUs on /dashboard</v>
+      </c>
+      <c r="D40" t="str">
+        <v>169 ms</v>
+      </c>
+      <c r="E40" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G40" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>WEB-PERF-040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Load Test with 100 VUs on /settings</v>
+      </c>
+      <c r="D41" t="str">
+        <v>284 ms</v>
+      </c>
+      <c r="E41" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G41" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>WEB-PERF-041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Load Test with 100 VUs on /search</v>
+      </c>
+      <c r="D42" t="str">
+        <v>271 ms</v>
+      </c>
+      <c r="E42" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G42" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>WEB-PERF-042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Load Test with 100 VUs on /</v>
+      </c>
+      <c r="D43" t="str">
+        <v>185 ms</v>
+      </c>
+      <c r="E43" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G43" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>WEB-PERF-043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Load Test with 100 VUs on /login</v>
+      </c>
+      <c r="D44" t="str">
+        <v>204 ms</v>
+      </c>
+      <c r="E44" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G44" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>WEB-PERF-044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Load Test with 100 VUs on /register</v>
+      </c>
+      <c r="D45" t="str">
+        <v>216 ms</v>
+      </c>
+      <c r="E45" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G45" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>WEB-PERF-045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Load Test with 100 VUs on /forgot-password</v>
+      </c>
+      <c r="D46" t="str">
+        <v>129 ms</v>
+      </c>
+      <c r="E46" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G46" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>WEB-PERF-046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Load Test with 100 VUs on /dashboard</v>
+      </c>
+      <c r="D47" t="str">
+        <v>257 ms</v>
+      </c>
+      <c r="E47" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G47" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>WEB-PERF-047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Load Test with 100 VUs on /settings</v>
+      </c>
+      <c r="D48" t="str">
+        <v>143 ms</v>
+      </c>
+      <c r="E48" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G48" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>WEB-PERF-048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Load Test with 100 VUs on /search</v>
+      </c>
+      <c r="D49" t="str">
+        <v>140 ms</v>
+      </c>
+      <c r="E49" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G49" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>WEB-PERF-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Load Test with 100 VUs on /</v>
+      </c>
+      <c r="D50" t="str">
+        <v>183 ms</v>
+      </c>
+      <c r="E50" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G50" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>WEB-PERF-050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Load Test with 100 VUs on /login</v>
+      </c>
+      <c r="D51" t="str">
+        <v>241 ms</v>
+      </c>
+      <c r="E51" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G51" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>WEB-PERF-051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Load Test with 100 VUs on /register</v>
+      </c>
+      <c r="D52" t="str">
+        <v>187 ms</v>
+      </c>
+      <c r="E52" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G52" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>WEB-PERF-052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Load Test with 100 VUs on /forgot-password</v>
+      </c>
+      <c r="D53" t="str">
+        <v>210 ms</v>
+      </c>
+      <c r="E53" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G53" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>WEB-PERF-053</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Load Test with 100 VUs on /dashboard</v>
+      </c>
+      <c r="D54" t="str">
+        <v>137 ms</v>
+      </c>
+      <c r="E54" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G54" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>WEB-PERF-054</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Load Test with 100 VUs on /settings</v>
+      </c>
+      <c r="D55" t="str">
+        <v>279 ms</v>
+      </c>
+      <c r="E55" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G55" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>WEB-PERF-055</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Load Test with 100 VUs on /search</v>
+      </c>
+      <c r="D56" t="str">
+        <v>259 ms</v>
+      </c>
+      <c r="E56" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G56" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>WEB-PERF-056</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Load Test with 100 VUs on /</v>
+      </c>
+      <c r="D57" t="str">
+        <v>147 ms</v>
+      </c>
+      <c r="E57" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F57" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G57" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>WEB-PERF-057</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Load Test with 100 VUs on /login</v>
+      </c>
+      <c r="D58" t="str">
+        <v>253 ms</v>
+      </c>
+      <c r="E58" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F58" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G58" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>WEB-PERF-058</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Load Test with 100 VUs on /register</v>
+      </c>
+      <c r="D59" t="str">
+        <v>272 ms</v>
+      </c>
+      <c r="E59" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F59" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G59" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>WEB-PERF-059</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Load Test with 100 VUs on /forgot-password</v>
+      </c>
+      <c r="D60" t="str">
+        <v>127 ms</v>
+      </c>
+      <c r="E60" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F60" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G60" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>WEB-PERF-060</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Load Test with 100 VUs on /dashboard</v>
+      </c>
+      <c r="D61" t="str">
+        <v>269 ms</v>
+      </c>
+      <c r="E61" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F61" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G61" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>WEB-PERF-061</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Load Test with 500 VUs on /settings</v>
+      </c>
+      <c r="D62" t="str">
+        <v>121 ms</v>
+      </c>
+      <c r="E62" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F62" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G62" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>WEB-PERF-062</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Load Test with 500 VUs on /search</v>
+      </c>
+      <c r="D63" t="str">
+        <v>224 ms</v>
+      </c>
+      <c r="E63" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F63" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G63" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>WEB-PERF-063</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Load Test with 500 VUs on /</v>
+      </c>
+      <c r="D64" t="str">
+        <v>201 ms</v>
+      </c>
+      <c r="E64" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F64" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G64" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>WEB-PERF-064</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Load Test with 500 VUs on /login</v>
+      </c>
+      <c r="D65" t="str">
+        <v>273 ms</v>
+      </c>
+      <c r="E65" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F65" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G65" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>WEB-PERF-065</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Load Test with 500 VUs on /register</v>
+      </c>
+      <c r="D66" t="str">
+        <v>182 ms</v>
+      </c>
+      <c r="E66" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F66" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G66" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>WEB-PERF-066</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Load Test with 500 VUs on /forgot-password</v>
+      </c>
+      <c r="D67" t="str">
+        <v>185 ms</v>
+      </c>
+      <c r="E67" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F67" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G67" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>WEB-PERF-067</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Load Test with 500 VUs on /dashboard</v>
+      </c>
+      <c r="D68" t="str">
+        <v>184 ms</v>
+      </c>
+      <c r="E68" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F68" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G68" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>WEB-PERF-068</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Load Test with 500 VUs on /settings</v>
+      </c>
+      <c r="D69" t="str">
+        <v>146 ms</v>
+      </c>
+      <c r="E69" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F69" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G69" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>WEB-PERF-069</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Load Test with 500 VUs on /search</v>
+      </c>
+      <c r="D70" t="str">
+        <v>175 ms</v>
+      </c>
+      <c r="E70" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F70" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G70" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>WEB-PERF-070</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Load Test with 500 VUs on /</v>
+      </c>
+      <c r="D71" t="str">
+        <v>117 ms</v>
+      </c>
+      <c r="E71" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F71" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G71" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>WEB-PERF-071</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Load Test with 500 VUs on /login</v>
+      </c>
+      <c r="D72" t="str">
+        <v>186 ms</v>
+      </c>
+      <c r="E72" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F72" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G72" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>WEB-PERF-072</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Load Test with 500 VUs on /register</v>
+      </c>
+      <c r="D73" t="str">
+        <v>190 ms</v>
+      </c>
+      <c r="E73" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F73" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G73" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>WEB-PERF-073</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Load Test with 500 VUs on /forgot-password</v>
+      </c>
+      <c r="D74" t="str">
+        <v>197 ms</v>
+      </c>
+      <c r="E74" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F74" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G74" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>WEB-PERF-074</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Load Test with 500 VUs on /dashboard</v>
+      </c>
+      <c r="D75" t="str">
+        <v>125 ms</v>
+      </c>
+      <c r="E75" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F75" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G75" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>WEB-PERF-075</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Load Test with 500 VUs on /settings</v>
+      </c>
+      <c r="D76" t="str">
+        <v>148 ms</v>
+      </c>
+      <c r="E76" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F76" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G76" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>WEB-PERF-076</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Load Test with 500 VUs on /search</v>
+      </c>
+      <c r="D77" t="str">
+        <v>123 ms</v>
+      </c>
+      <c r="E77" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F77" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G77" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>WEB-PERF-077</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Load Test with 500 VUs on /</v>
+      </c>
+      <c r="D78" t="str">
+        <v>280 ms</v>
+      </c>
+      <c r="E78" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F78" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G78" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>WEB-PERF-078</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Load Test with 500 VUs on /login</v>
+      </c>
+      <c r="D79" t="str">
+        <v>160 ms</v>
+      </c>
+      <c r="E79" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F79" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G79" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>WEB-PERF-079</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Load Test with 500 VUs on /register</v>
+      </c>
+      <c r="D80" t="str">
+        <v>237 ms</v>
+      </c>
+      <c r="E80" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F80" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G80" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>WEB-PERF-080</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Load Test with 500 VUs on /forgot-password</v>
+      </c>
+      <c r="D81" t="str">
+        <v>127 ms</v>
+      </c>
+      <c r="E81" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F81" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G81" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>WEB-PERF-081</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Load Test with 500 VUs on /dashboard</v>
+      </c>
+      <c r="D82" t="str">
+        <v>107 ms</v>
+      </c>
+      <c r="E82" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F82" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G82" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>WEB-PERF-082</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Load Test with 500 VUs on /settings</v>
+      </c>
+      <c r="D83" t="str">
+        <v>208 ms</v>
+      </c>
+      <c r="E83" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F83" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G83" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>WEB-PERF-083</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Load Test with 500 VUs on /search</v>
+      </c>
+      <c r="D84" t="str">
+        <v>225 ms</v>
+      </c>
+      <c r="E84" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F84" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G84" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>WEB-PERF-084</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Load Test with 500 VUs on /</v>
+      </c>
+      <c r="D85" t="str">
+        <v>200 ms</v>
+      </c>
+      <c r="E85" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F85" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G85" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>WEB-PERF-085</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Load Test with 500 VUs on /login</v>
+      </c>
+      <c r="D86" t="str">
+        <v>274 ms</v>
+      </c>
+      <c r="E86" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F86" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G86" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>WEB-PERF-086</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Load Test with 500 VUs on /register</v>
+      </c>
+      <c r="D87" t="str">
+        <v>213 ms</v>
+      </c>
+      <c r="E87" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F87" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G87" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>WEB-PERF-087</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Load Test with 500 VUs on /forgot-password</v>
+      </c>
+      <c r="D88" t="str">
+        <v>152 ms</v>
+      </c>
+      <c r="E88" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F88" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G88" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>WEB-PERF-088</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Load Test with 500 VUs on /dashboard</v>
+      </c>
+      <c r="D89" t="str">
+        <v>245 ms</v>
+      </c>
+      <c r="E89" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F89" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G89" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>WEB-PERF-089</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Load Test with 500 VUs on /settings</v>
+      </c>
+      <c r="D90" t="str">
+        <v>106 ms</v>
+      </c>
+      <c r="E90" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F90" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G90" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>WEB-PERF-090</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Load Test with 500 VUs on /search</v>
+      </c>
+      <c r="D91" t="str">
+        <v>141 ms</v>
+      </c>
+      <c r="E91" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F91" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G91" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>WEB-PERF-091</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Load Test with 500 VUs on /</v>
+      </c>
+      <c r="D92" t="str">
+        <v>290 ms</v>
+      </c>
+      <c r="E92" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F92" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G92" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>WEB-PERF-092</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Load Test with 500 VUs on /login</v>
+      </c>
+      <c r="D93" t="str">
+        <v>257 ms</v>
+      </c>
+      <c r="E93" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F93" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G93" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>WEB-PERF-093</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Load Test with 500 VUs on /register</v>
+      </c>
+      <c r="D94" t="str">
+        <v>294 ms</v>
+      </c>
+      <c r="E94" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F94" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G94" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>WEB-PERF-094</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Load Test with 500 VUs on /forgot-password</v>
+      </c>
+      <c r="D95" t="str">
+        <v>124 ms</v>
+      </c>
+      <c r="E95" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F95" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G95" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>WEB-PERF-095</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Load Test with 500 VUs on /dashboard</v>
+      </c>
+      <c r="D96" t="str">
+        <v>243 ms</v>
+      </c>
+      <c r="E96" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F96" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G96" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>WEB-PERF-096</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Load Test with 500 VUs on /settings</v>
+      </c>
+      <c r="D97" t="str">
+        <v>134 ms</v>
+      </c>
+      <c r="E97" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F97" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G97" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>WEB-PERF-097</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Load Test with 500 VUs on /search</v>
+      </c>
+      <c r="D98" t="str">
+        <v>257 ms</v>
+      </c>
+      <c r="E98" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F98" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G98" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>WEB-PERF-098</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Load Test with 500 VUs on /</v>
+      </c>
+      <c r="D99" t="str">
+        <v>187 ms</v>
+      </c>
+      <c r="E99" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F99" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G99" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>WEB-PERF-099</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Load Test with 500 VUs on /login</v>
+      </c>
+      <c r="D100" t="str">
+        <v>183 ms</v>
+      </c>
+      <c r="E100" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F100" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G100" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>WEB-PERF-100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Load Test with 500 VUs on /register</v>
+      </c>
+      <c r="D101" t="str">
+        <v>130 ms</v>
+      </c>
+      <c r="E101" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F101" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G101" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>WEB-PERF-101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Load Test with 500 VUs on /forgot-password</v>
+      </c>
+      <c r="D102" t="str">
+        <v>112 ms</v>
+      </c>
+      <c r="E102" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F102" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G102" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>WEB-PERF-102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Load Test with 500 VUs on /dashboard</v>
+      </c>
+      <c r="D103" t="str">
+        <v>187 ms</v>
+      </c>
+      <c r="E103" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F103" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G103" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>WEB-PERF-103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Load Test with 500 VUs on /settings</v>
+      </c>
+      <c r="D104" t="str">
+        <v>186 ms</v>
+      </c>
+      <c r="E104" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F104" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G104" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>WEB-PERF-104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Load Test with 500 VUs on /search</v>
+      </c>
+      <c r="D105" t="str">
+        <v>252 ms</v>
+      </c>
+      <c r="E105" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F105" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G105" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>WEB-PERF-105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Load Test with 500 VUs on /</v>
+      </c>
+      <c r="D106" t="str">
+        <v>227 ms</v>
+      </c>
+      <c r="E106" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F106" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G106" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>WEB-PERF-106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Load Test with 500 VUs on /login</v>
+      </c>
+      <c r="D107" t="str">
+        <v>245 ms</v>
+      </c>
+      <c r="E107" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F107" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G107" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>WEB-PERF-107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C108" t="str">
+        <v>Load Test with 500 VUs on /register</v>
+      </c>
+      <c r="D108" t="str">
+        <v>118 ms</v>
+      </c>
+      <c r="E108" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F108" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G108" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>WEB-PERF-108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C109" t="str">
+        <v>Load Test with 500 VUs on /forgot-password</v>
+      </c>
+      <c r="D109" t="str">
+        <v>239 ms</v>
+      </c>
+      <c r="E109" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F109" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G109" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>WEB-PERF-109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C110" t="str">
+        <v>Load Test with 500 VUs on /dashboard</v>
+      </c>
+      <c r="D110" t="str">
+        <v>240 ms</v>
+      </c>
+      <c r="E110" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F110" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G110" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>WEB-PERF-110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C111" t="str">
+        <v>Load Test with 500 VUs on /settings</v>
+      </c>
+      <c r="D111" t="str">
+        <v>242 ms</v>
+      </c>
+      <c r="E111" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F111" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G111" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>WEB-PERF-111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C112" t="str">
+        <v>Load Test with 500 VUs on /search</v>
+      </c>
+      <c r="D112" t="str">
+        <v>103 ms</v>
+      </c>
+      <c r="E112" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F112" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G112" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>WEB-PERF-112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C113" t="str">
+        <v>Load Test with 500 VUs on /</v>
+      </c>
+      <c r="D113" t="str">
+        <v>170 ms</v>
+      </c>
+      <c r="E113" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F113" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G113" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>WEB-PERF-113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C114" t="str">
+        <v>Load Test with 500 VUs on /login</v>
+      </c>
+      <c r="D114" t="str">
+        <v>104 ms</v>
+      </c>
+      <c r="E114" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F114" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G114" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>WEB-PERF-114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C115" t="str">
+        <v>Load Test with 500 VUs on /register</v>
+      </c>
+      <c r="D115" t="str">
+        <v>123 ms</v>
+      </c>
+      <c r="E115" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F115" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G115" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>WEB-PERF-115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C116" t="str">
+        <v>Load Test with 500 VUs on /forgot-password</v>
+      </c>
+      <c r="D116" t="str">
+        <v>181 ms</v>
+      </c>
+      <c r="E116" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F116" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G116" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>WEB-PERF-116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Load Test with 500 VUs on /dashboard</v>
+      </c>
+      <c r="D117" t="str">
+        <v>234 ms</v>
+      </c>
+      <c r="E117" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F117" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G117" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>WEB-PERF-117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C118" t="str">
+        <v>Load Test with 500 VUs on /settings</v>
+      </c>
+      <c r="D118" t="str">
+        <v>211 ms</v>
+      </c>
+      <c r="E118" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F118" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G118" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>WEB-PERF-118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C119" t="str">
+        <v>Load Test with 500 VUs on /search</v>
+      </c>
+      <c r="D119" t="str">
+        <v>266 ms</v>
+      </c>
+      <c r="E119" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F119" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G119" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>WEB-PERF-119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C120" t="str">
+        <v>Load Test with 500 VUs on /</v>
+      </c>
+      <c r="D120" t="str">
+        <v>285 ms</v>
+      </c>
+      <c r="E120" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F120" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G120" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>WEB-PERF-120</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C121" t="str">
+        <v>Load Test with 500 VUs on /login</v>
+      </c>
+      <c r="D121" t="str">
+        <v>163 ms</v>
+      </c>
+      <c r="E121" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F121" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G121" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>WEB-PERF-121</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C122" t="str">
+        <v>Load Test with 1000 VUs on /register</v>
+      </c>
+      <c r="D122" t="str">
+        <v>187 ms</v>
+      </c>
+      <c r="E122" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F122" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G122" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>WEB-PERF-122</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C123" t="str">
+        <v>Load Test with 1000 VUs on /forgot-password</v>
+      </c>
+      <c r="D123" t="str">
+        <v>122 ms</v>
+      </c>
+      <c r="E123" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F123" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G123" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>WEB-PERF-123</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C124" t="str">
+        <v>Load Test with 1000 VUs on /dashboard</v>
+      </c>
+      <c r="D124" t="str">
+        <v>253 ms</v>
+      </c>
+      <c r="E124" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F124" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G124" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>WEB-PERF-124</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C125" t="str">
+        <v>Load Test with 1000 VUs on /settings</v>
+      </c>
+      <c r="D125" t="str">
+        <v>105 ms</v>
+      </c>
+      <c r="E125" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F125" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G125" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>WEB-PERF-125</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C126" t="str">
+        <v>Load Test with 1000 VUs on /search</v>
+      </c>
+      <c r="D126" t="str">
+        <v>143 ms</v>
+      </c>
+      <c r="E126" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F126" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G126" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>WEB-PERF-126</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Load Test with 1000 VUs on /</v>
+      </c>
+      <c r="D127" t="str">
+        <v>165 ms</v>
+      </c>
+      <c r="E127" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F127" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G127" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>WEB-PERF-127</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Load Test with 1000 VUs on /login</v>
+      </c>
+      <c r="D128" t="str">
+        <v>242 ms</v>
+      </c>
+      <c r="E128" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F128" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G128" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>WEB-PERF-128</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Load Test with 1000 VUs on /register</v>
+      </c>
+      <c r="D129" t="str">
+        <v>271 ms</v>
+      </c>
+      <c r="E129" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F129" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G129" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>WEB-PERF-129</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Load Test with 1000 VUs on /forgot-password</v>
+      </c>
+      <c r="D130" t="str">
+        <v>176 ms</v>
+      </c>
+      <c r="E130" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F130" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G130" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>WEB-PERF-130</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Load Test with 1000 VUs on /dashboard</v>
+      </c>
+      <c r="D131" t="str">
+        <v>167 ms</v>
+      </c>
+      <c r="E131" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F131" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G131" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>WEB-PERF-131</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C132" t="str">
+        <v>Load Test with 1000 VUs on /settings</v>
+      </c>
+      <c r="D132" t="str">
+        <v>249 ms</v>
+      </c>
+      <c r="E132" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F132" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G132" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>WEB-PERF-132</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Load Test with 1000 VUs on /search</v>
+      </c>
+      <c r="D133" t="str">
+        <v>235 ms</v>
+      </c>
+      <c r="E133" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F133" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G133" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>WEB-PERF-133</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C134" t="str">
+        <v>Load Test with 1000 VUs on /</v>
+      </c>
+      <c r="D134" t="str">
+        <v>142 ms</v>
+      </c>
+      <c r="E134" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F134" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G134" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>WEB-PERF-134</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C135" t="str">
+        <v>Load Test with 1000 VUs on /login</v>
+      </c>
+      <c r="D135" t="str">
+        <v>274 ms</v>
+      </c>
+      <c r="E135" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F135" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G135" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>WEB-PERF-135</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C136" t="str">
+        <v>Load Test with 1000 VUs on /register</v>
+      </c>
+      <c r="D136" t="str">
+        <v>296 ms</v>
+      </c>
+      <c r="E136" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F136" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G136" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>WEB-PERF-136</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C137" t="str">
+        <v>Load Test with 1000 VUs on /forgot-password</v>
+      </c>
+      <c r="D137" t="str">
+        <v>170 ms</v>
+      </c>
+      <c r="E137" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F137" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G137" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>WEB-PERF-137</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C138" t="str">
+        <v>Load Test with 1000 VUs on /dashboard</v>
+      </c>
+      <c r="D138" t="str">
+        <v>273 ms</v>
+      </c>
+      <c r="E138" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F138" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G138" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>WEB-PERF-138</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C139" t="str">
+        <v>Load Test with 1000 VUs on /settings</v>
+      </c>
+      <c r="D139" t="str">
+        <v>134 ms</v>
+      </c>
+      <c r="E139" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F139" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G139" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>WEB-PERF-139</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C140" t="str">
+        <v>Load Test with 1000 VUs on /search</v>
+      </c>
+      <c r="D140" t="str">
+        <v>205 ms</v>
+      </c>
+      <c r="E140" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F140" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G140" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>WEB-PERF-140</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C141" t="str">
+        <v>Load Test with 1000 VUs on /</v>
+      </c>
+      <c r="D141" t="str">
+        <v>157 ms</v>
+      </c>
+      <c r="E141" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F141" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G141" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>WEB-PERF-141</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C142" t="str">
+        <v>Load Test with 1000 VUs on /login</v>
+      </c>
+      <c r="D142" t="str">
+        <v>159 ms</v>
+      </c>
+      <c r="E142" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F142" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G142" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>WEB-PERF-142</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C143" t="str">
+        <v>Load Test with 1000 VUs on /register</v>
+      </c>
+      <c r="D143" t="str">
+        <v>220 ms</v>
+      </c>
+      <c r="E143" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F143" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G143" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>WEB-PERF-143</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C144" t="str">
+        <v>Load Test with 1000 VUs on /forgot-password</v>
+      </c>
+      <c r="D144" t="str">
+        <v>189 ms</v>
+      </c>
+      <c r="E144" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F144" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G144" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>WEB-PERF-144</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C145" t="str">
+        <v>Load Test with 1000 VUs on /dashboard</v>
+      </c>
+      <c r="D145" t="str">
+        <v>140 ms</v>
+      </c>
+      <c r="E145" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F145" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G145" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>WEB-PERF-145</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C146" t="str">
+        <v>Load Test with 1000 VUs on /settings</v>
+      </c>
+      <c r="D146" t="str">
+        <v>121 ms</v>
+      </c>
+      <c r="E146" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F146" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G146" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>WEB-PERF-146</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C147" t="str">
+        <v>Load Test with 1000 VUs on /search</v>
+      </c>
+      <c r="D147" t="str">
+        <v>204 ms</v>
+      </c>
+      <c r="E147" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F147" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G147" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>WEB-PERF-147</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C148" t="str">
+        <v>Load Test with 1000 VUs on /</v>
+      </c>
+      <c r="D148" t="str">
+        <v>159 ms</v>
+      </c>
+      <c r="E148" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F148" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G148" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>WEB-PERF-148</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C149" t="str">
+        <v>Load Test with 1000 VUs on /login</v>
+      </c>
+      <c r="D149" t="str">
+        <v>227 ms</v>
+      </c>
+      <c r="E149" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F149" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G149" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>WEB-PERF-149</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C150" t="str">
+        <v>Load Test with 1000 VUs on /register</v>
+      </c>
+      <c r="D150" t="str">
+        <v>298 ms</v>
+      </c>
+      <c r="E150" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F150" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G150" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>WEB-PERF-150</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C151" t="str">
+        <v>Load Test with 1000 VUs on /forgot-password</v>
+      </c>
+      <c r="D151" t="str">
+        <v>195 ms</v>
+      </c>
+      <c r="E151" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F151" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G151" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>WEB-PERF-151</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C152" t="str">
+        <v>Load Test with 1000 VUs on /dashboard</v>
+      </c>
+      <c r="D152" t="str">
+        <v>294 ms</v>
+      </c>
+      <c r="E152" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F152" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G152" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>WEB-PERF-152</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C153" t="str">
+        <v>Load Test with 1000 VUs on /settings</v>
+      </c>
+      <c r="D153" t="str">
+        <v>141 ms</v>
+      </c>
+      <c r="E153" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F153" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G153" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>WEB-PERF-153</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C154" t="str">
+        <v>Load Test with 1000 VUs on /search</v>
+      </c>
+      <c r="D154" t="str">
+        <v>132 ms</v>
+      </c>
+      <c r="E154" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F154" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G154" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>WEB-PERF-154</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C155" t="str">
+        <v>Load Test with 1000 VUs on /</v>
+      </c>
+      <c r="D155" t="str">
+        <v>299 ms</v>
+      </c>
+      <c r="E155" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F155" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G155" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>WEB-PERF-155</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C156" t="str">
+        <v>Load Test with 1000 VUs on /login</v>
+      </c>
+      <c r="D156" t="str">
+        <v>169 ms</v>
+      </c>
+      <c r="E156" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F156" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G156" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>WEB-PERF-156</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C157" t="str">
+        <v>Load Test with 1000 VUs on /register</v>
+      </c>
+      <c r="D157" t="str">
+        <v>197 ms</v>
+      </c>
+      <c r="E157" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F157" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G157" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>WEB-PERF-157</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C158" t="str">
+        <v>Load Test with 1000 VUs on /forgot-password</v>
+      </c>
+      <c r="D158" t="str">
+        <v>182 ms</v>
+      </c>
+      <c r="E158" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F158" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G158" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>WEB-PERF-158</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C159" t="str">
+        <v>Load Test with 1000 VUs on /dashboard</v>
+      </c>
+      <c r="D159" t="str">
+        <v>132 ms</v>
+      </c>
+      <c r="E159" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F159" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G159" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>WEB-PERF-159</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C160" t="str">
+        <v>Load Test with 1000 VUs on /settings</v>
+      </c>
+      <c r="D160" t="str">
+        <v>138 ms</v>
+      </c>
+      <c r="E160" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F160" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G160" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>WEB-PERF-160</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C161" t="str">
+        <v>Load Test with 1000 VUs on /search</v>
+      </c>
+      <c r="D161" t="str">
+        <v>180 ms</v>
+      </c>
+      <c r="E161" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F161" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G161" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>WEB-PERF-161</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C162" t="str">
+        <v>Load Test with 1000 VUs on /</v>
+      </c>
+      <c r="D162" t="str">
+        <v>130 ms</v>
+      </c>
+      <c r="E162" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F162" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G162" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>WEB-PERF-162</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C163" t="str">
+        <v>Load Test with 1000 VUs on /login</v>
+      </c>
+      <c r="D163" t="str">
+        <v>287 ms</v>
+      </c>
+      <c r="E163" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F163" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G163" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>WEB-PERF-163</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C164" t="str">
+        <v>Load Test with 1000 VUs on /register</v>
+      </c>
+      <c r="D164" t="str">
+        <v>294 ms</v>
+      </c>
+      <c r="E164" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F164" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G164" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>WEB-PERF-164</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C165" t="str">
+        <v>Load Test with 1000 VUs on /forgot-password</v>
+      </c>
+      <c r="D165" t="str">
+        <v>269 ms</v>
+      </c>
+      <c r="E165" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F165" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G165" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>WEB-PERF-165</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C166" t="str">
+        <v>Load Test with 1000 VUs on /dashboard</v>
+      </c>
+      <c r="D166" t="str">
+        <v>160 ms</v>
+      </c>
+      <c r="E166" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F166" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G166" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>WEB-PERF-166</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C167" t="str">
+        <v>Load Test with 1000 VUs on /settings</v>
+      </c>
+      <c r="D167" t="str">
+        <v>287 ms</v>
+      </c>
+      <c r="E167" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F167" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G167" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>WEB-PERF-167</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C168" t="str">
+        <v>Load Test with 1000 VUs on /search</v>
+      </c>
+      <c r="D168" t="str">
+        <v>283 ms</v>
+      </c>
+      <c r="E168" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F168" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G168" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>WEB-PERF-168</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C169" t="str">
+        <v>Load Test with 1000 VUs on /</v>
+      </c>
+      <c r="D169" t="str">
+        <v>143 ms</v>
+      </c>
+      <c r="E169" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F169" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G169" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>WEB-PERF-169</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C170" t="str">
+        <v>Load Test with 1000 VUs on /login</v>
+      </c>
+      <c r="D170" t="str">
+        <v>239 ms</v>
+      </c>
+      <c r="E170" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F170" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G170" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>WEB-PERF-170</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C171" t="str">
+        <v>Load Test with 1000 VUs on /register</v>
+      </c>
+      <c r="D171" t="str">
+        <v>220 ms</v>
+      </c>
+      <c r="E171" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F171" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G171" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>WEB-PERF-171</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C172" t="str">
+        <v>Load Test with 1000 VUs on /forgot-password</v>
+      </c>
+      <c r="D172" t="str">
+        <v>177 ms</v>
+      </c>
+      <c r="E172" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F172" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G172" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>WEB-PERF-172</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C173" t="str">
+        <v>Load Test with 1000 VUs on /dashboard</v>
+      </c>
+      <c r="D173" t="str">
+        <v>276 ms</v>
+      </c>
+      <c r="E173" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F173" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G173" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>WEB-PERF-173</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C174" t="str">
+        <v>Load Test with 1000 VUs on /settings</v>
+      </c>
+      <c r="D174" t="str">
+        <v>297 ms</v>
+      </c>
+      <c r="E174" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F174" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G174" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>WEB-PERF-174</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C175" t="str">
+        <v>Load Test with 1000 VUs on /search</v>
+      </c>
+      <c r="D175" t="str">
+        <v>140 ms</v>
+      </c>
+      <c r="E175" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F175" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G175" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>WEB-PERF-175</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C176" t="str">
+        <v>Load Test with 1000 VUs on /</v>
+      </c>
+      <c r="D176" t="str">
+        <v>277 ms</v>
+      </c>
+      <c r="E176" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F176" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G176" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>WEB-PERF-176</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C177" t="str">
+        <v>Load Test with 1000 VUs on /login</v>
+      </c>
+      <c r="D177" t="str">
+        <v>256 ms</v>
+      </c>
+      <c r="E177" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F177" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G177" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>WEB-PERF-177</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C178" t="str">
+        <v>Load Test with 1000 VUs on /register</v>
+      </c>
+      <c r="D178" t="str">
+        <v>243 ms</v>
+      </c>
+      <c r="E178" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F178" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G178" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>WEB-PERF-178</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C179" t="str">
+        <v>Load Test with 1000 VUs on /forgot-password</v>
+      </c>
+      <c r="D179" t="str">
+        <v>108 ms</v>
+      </c>
+      <c r="E179" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F179" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G179" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>WEB-PERF-179</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C180" t="str">
+        <v>Load Test with 1000 VUs on /dashboard</v>
+      </c>
+      <c r="D180" t="str">
+        <v>222 ms</v>
+      </c>
+      <c r="E180" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F180" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G180" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>WEB-PERF-180</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C181" t="str">
+        <v>Load Test with 1000 VUs on /settings</v>
+      </c>
+      <c r="D181" t="str">
+        <v>254 ms</v>
+      </c>
+      <c r="E181" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F181" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G181" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>WEB-PERF-181</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C182" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /search</v>
+      </c>
+      <c r="D182" t="str">
+        <v>265 ms</v>
+      </c>
+      <c r="E182" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F182" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G182" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>WEB-PERF-182</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C183" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /</v>
+      </c>
+      <c r="D183" t="str">
+        <v>102 ms</v>
+      </c>
+      <c r="E183" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F183" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G183" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>WEB-PERF-183</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C184" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /login</v>
+      </c>
+      <c r="D184" t="str">
+        <v>121 ms</v>
+      </c>
+      <c r="E184" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F184" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G184" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>WEB-PERF-184</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C185" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /register</v>
+      </c>
+      <c r="D185" t="str">
+        <v>127 ms</v>
+      </c>
+      <c r="E185" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F185" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G185" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>WEB-PERF-185</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C186" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /forgot-password</v>
+      </c>
+      <c r="D186" t="str">
+        <v>295 ms</v>
+      </c>
+      <c r="E186" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F186" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G186" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>WEB-PERF-186</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C187" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /dashboard</v>
+      </c>
+      <c r="D187" t="str">
+        <v>294 ms</v>
+      </c>
+      <c r="E187" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F187" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G187" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>WEB-PERF-187</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C188" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /settings</v>
+      </c>
+      <c r="D188" t="str">
+        <v>286 ms</v>
+      </c>
+      <c r="E188" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F188" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G188" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>WEB-PERF-188</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C189" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /search</v>
+      </c>
+      <c r="D189" t="str">
+        <v>182 ms</v>
+      </c>
+      <c r="E189" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F189" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G189" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>WEB-PERF-189</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C190" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /</v>
+      </c>
+      <c r="D190" t="str">
+        <v>138 ms</v>
+      </c>
+      <c r="E190" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F190" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G190" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>WEB-PERF-190</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C191" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /login</v>
+      </c>
+      <c r="D191" t="str">
+        <v>103 ms</v>
+      </c>
+      <c r="E191" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F191" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G191" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>WEB-PERF-191</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C192" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /register</v>
+      </c>
+      <c r="D192" t="str">
+        <v>142 ms</v>
+      </c>
+      <c r="E192" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F192" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G192" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>WEB-PERF-192</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C193" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /forgot-password</v>
+      </c>
+      <c r="D193" t="str">
+        <v>107 ms</v>
+      </c>
+      <c r="E193" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F193" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G193" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>WEB-PERF-193</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C194" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /dashboard</v>
+      </c>
+      <c r="D194" t="str">
+        <v>117 ms</v>
+      </c>
+      <c r="E194" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F194" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G194" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>WEB-PERF-194</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /settings</v>
+      </c>
+      <c r="D195" t="str">
+        <v>159 ms</v>
+      </c>
+      <c r="E195" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F195" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G195" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>WEB-PERF-195</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /search</v>
+      </c>
+      <c r="D196" t="str">
+        <v>149 ms</v>
+      </c>
+      <c r="E196" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F196" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G196" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>WEB-PERF-196</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /</v>
+      </c>
+      <c r="D197" t="str">
+        <v>235 ms</v>
+      </c>
+      <c r="E197" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F197" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G197" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>WEB-PERF-197</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /login</v>
+      </c>
+      <c r="D198" t="str">
+        <v>102 ms</v>
+      </c>
+      <c r="E198" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F198" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G198" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>WEB-PERF-198</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /register</v>
+      </c>
+      <c r="D199" t="str">
+        <v>196 ms</v>
+      </c>
+      <c r="E199" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F199" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G199" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>WEB-PERF-199</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /forgot-password</v>
+      </c>
+      <c r="D200" t="str">
+        <v>121 ms</v>
+      </c>
+      <c r="E200" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F200" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G200" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>WEB-PERF-200</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Web Load</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Load Test with Stress/Spike/Endurance VUs on /dashboard</v>
+      </c>
+      <c r="D201" t="str">
+        <v>276 ms</v>
+      </c>
+      <c r="E201" t="str">
+        <v>&lt; 400 ms</v>
+      </c>
+      <c r="F201" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G201" t="str">
         <v>PASSED</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G201"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:G201"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Test Case ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Type</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Scenario</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Measured Latency</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Threshold</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Result</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Status</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>AND-PERF-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C2" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D2" t="str">
+        <v>133 ms</v>
+      </c>
+      <c r="E2" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F2" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G2" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AND-PERF-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C3" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D3" t="str">
+        <v>97 ms</v>
+      </c>
+      <c r="E3" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F3" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G3" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>AND-PERF-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C4" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D4" t="str">
+        <v>216 ms</v>
+      </c>
+      <c r="E4" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F4" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G4" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>AND-PERF-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C5" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D5" t="str">
+        <v>213 ms</v>
+      </c>
+      <c r="E5" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F5" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G5" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>AND-PERF-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C6" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D6" t="str">
+        <v>151 ms</v>
+      </c>
+      <c r="E6" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F6" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G6" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AND-PERF-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C7" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D7" t="str">
+        <v>89 ms</v>
+      </c>
+      <c r="E7" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F7" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G7" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AND-PERF-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C8" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D8" t="str">
+        <v>170 ms</v>
+      </c>
+      <c r="E8" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F8" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G8" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AND-PERF-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C9" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D9" t="str">
+        <v>213 ms</v>
+      </c>
+      <c r="E9" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G9" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AND-PERF-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C10" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D10" t="str">
+        <v>87 ms</v>
+      </c>
+      <c r="E10" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G10" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AND-PERF-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C11" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D11" t="str">
+        <v>214 ms</v>
+      </c>
+      <c r="E11" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G11" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>AND-PERF-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C12" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D12" t="str">
+        <v>162 ms</v>
+      </c>
+      <c r="E12" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G12" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>AND-PERF-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C13" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D13" t="str">
+        <v>129 ms</v>
+      </c>
+      <c r="E13" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G13" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>AND-PERF-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C14" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D14" t="str">
+        <v>123 ms</v>
+      </c>
+      <c r="E14" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G14" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>AND-PERF-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C15" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D15" t="str">
+        <v>91 ms</v>
+      </c>
+      <c r="E15" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G15" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>AND-PERF-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C16" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D16" t="str">
+        <v>155 ms</v>
+      </c>
+      <c r="E16" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G16" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>AND-PERF-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C17" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D17" t="str">
+        <v>104 ms</v>
+      </c>
+      <c r="E17" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G17" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>AND-PERF-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C18" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D18" t="str">
+        <v>97 ms</v>
+      </c>
+      <c r="E18" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G18" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>AND-PERF-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C19" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D19" t="str">
+        <v>195 ms</v>
+      </c>
+      <c r="E19" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G19" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>AND-PERF-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C20" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D20" t="str">
+        <v>85 ms</v>
+      </c>
+      <c r="E20" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G20" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>AND-PERF-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C21" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D21" t="str">
+        <v>221 ms</v>
+      </c>
+      <c r="E21" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G21" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>AND-PERF-021</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C22" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D22" t="str">
+        <v>139 ms</v>
+      </c>
+      <c r="E22" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G22" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>AND-PERF-022</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C23" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D23" t="str">
+        <v>176 ms</v>
+      </c>
+      <c r="E23" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F23" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G23" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>AND-PERF-023</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C24" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D24" t="str">
+        <v>129 ms</v>
+      </c>
+      <c r="E24" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F24" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G24" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>AND-PERF-024</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C25" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D25" t="str">
+        <v>189 ms</v>
+      </c>
+      <c r="E25" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F25" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G25" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>AND-PERF-025</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C26" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D26" t="str">
+        <v>183 ms</v>
+      </c>
+      <c r="E26" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F26" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G26" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>AND-PERF-026</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C27" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D27" t="str">
+        <v>99 ms</v>
+      </c>
+      <c r="E27" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F27" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G27" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>AND-PERF-027</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C28" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D28" t="str">
+        <v>187 ms</v>
+      </c>
+      <c r="E28" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F28" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G28" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>AND-PERF-028</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C29" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D29" t="str">
+        <v>225 ms</v>
+      </c>
+      <c r="E29" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F29" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G29" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>AND-PERF-029</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C30" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D30" t="str">
+        <v>97 ms</v>
+      </c>
+      <c r="E30" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F30" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G30" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>AND-PERF-030</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C31" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D31" t="str">
+        <v>220 ms</v>
+      </c>
+      <c r="E31" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F31" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G31" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>AND-PERF-031</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C32" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D32" t="str">
+        <v>140 ms</v>
+      </c>
+      <c r="E32" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F32" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G32" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>AND-PERF-032</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C33" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D33" t="str">
+        <v>81 ms</v>
+      </c>
+      <c r="E33" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F33" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G33" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>AND-PERF-033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C34" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D34" t="str">
+        <v>213 ms</v>
+      </c>
+      <c r="E34" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F34" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G34" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>AND-PERF-034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C35" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D35" t="str">
+        <v>133 ms</v>
+      </c>
+      <c r="E35" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F35" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G35" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>AND-PERF-035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C36" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D36" t="str">
+        <v>182 ms</v>
+      </c>
+      <c r="E36" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F36" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G36" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>AND-PERF-036</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C37" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D37" t="str">
+        <v>222 ms</v>
+      </c>
+      <c r="E37" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F37" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G37" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>AND-PERF-037</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C38" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D38" t="str">
+        <v>92 ms</v>
+      </c>
+      <c r="E38" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F38" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G38" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>AND-PERF-038</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C39" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D39" t="str">
+        <v>102 ms</v>
+      </c>
+      <c r="E39" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F39" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G39" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>AND-PERF-039</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C40" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D40" t="str">
+        <v>139 ms</v>
+      </c>
+      <c r="E40" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F40" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G40" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>AND-PERF-040</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C41" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D41" t="str">
+        <v>165 ms</v>
+      </c>
+      <c r="E41" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F41" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G41" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>AND-PERF-041</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C42" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D42" t="str">
+        <v>227 ms</v>
+      </c>
+      <c r="E42" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F42" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G42" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>AND-PERF-042</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C43" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D43" t="str">
+        <v>210 ms</v>
+      </c>
+      <c r="E43" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F43" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G43" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>AND-PERF-043</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C44" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D44" t="str">
+        <v>136 ms</v>
+      </c>
+      <c r="E44" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F44" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G44" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>AND-PERF-044</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C45" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D45" t="str">
+        <v>114 ms</v>
+      </c>
+      <c r="E45" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F45" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G45" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>AND-PERF-045</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C46" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D46" t="str">
+        <v>182 ms</v>
+      </c>
+      <c r="E46" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F46" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G46" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>AND-PERF-046</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C47" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D47" t="str">
+        <v>203 ms</v>
+      </c>
+      <c r="E47" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F47" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G47" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>AND-PERF-047</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C48" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D48" t="str">
+        <v>135 ms</v>
+      </c>
+      <c r="E48" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F48" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G48" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>AND-PERF-048</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C49" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D49" t="str">
+        <v>91 ms</v>
+      </c>
+      <c r="E49" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F49" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G49" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>AND-PERF-049</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C50" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D50" t="str">
+        <v>186 ms</v>
+      </c>
+      <c r="E50" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F50" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G50" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>AND-PERF-050</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C51" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D51" t="str">
+        <v>88 ms</v>
+      </c>
+      <c r="E51" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F51" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G51" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>AND-PERF-051</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C52" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D52" t="str">
+        <v>143 ms</v>
+      </c>
+      <c r="E52" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F52" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G52" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>AND-PERF-052</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C53" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D53" t="str">
+        <v>177 ms</v>
+      </c>
+      <c r="E53" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F53" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G53" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>AND-PERF-053</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C54" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D54" t="str">
+        <v>82 ms</v>
+      </c>
+      <c r="E54" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F54" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G54" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>AND-PERF-054</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C55" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D55" t="str">
+        <v>164 ms</v>
+      </c>
+      <c r="E55" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F55" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G55" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>AND-PERF-055</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C56" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D56" t="str">
+        <v>215 ms</v>
+      </c>
+      <c r="E56" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F56" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G56" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>AND-PERF-056</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C57" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D57" t="str">
+        <v>158 ms</v>
+      </c>
+      <c r="E57" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F57" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G57" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>AND-PERF-057</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C58" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D58" t="str">
+        <v>218 ms</v>
+      </c>
+      <c r="E58" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F58" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G58" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>AND-PERF-058</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C59" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D59" t="str">
+        <v>82 ms</v>
+      </c>
+      <c r="E59" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F59" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G59" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>AND-PERF-059</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C60" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D60" t="str">
+        <v>199 ms</v>
+      </c>
+      <c r="E60" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F60" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G60" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>AND-PERF-060</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C61" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D61" t="str">
+        <v>149 ms</v>
+      </c>
+      <c r="E61" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F61" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G61" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>AND-PERF-061</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C62" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D62" t="str">
+        <v>154 ms</v>
+      </c>
+      <c r="E62" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F62" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G62" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>AND-PERF-062</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C63" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D63" t="str">
+        <v>224 ms</v>
+      </c>
+      <c r="E63" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F63" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G63" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>AND-PERF-063</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C64" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D64" t="str">
+        <v>220 ms</v>
+      </c>
+      <c r="E64" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F64" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G64" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>AND-PERF-064</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C65" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D65" t="str">
+        <v>90 ms</v>
+      </c>
+      <c r="E65" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F65" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G65" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>AND-PERF-065</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C66" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D66" t="str">
+        <v>222 ms</v>
+      </c>
+      <c r="E66" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F66" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G66" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>AND-PERF-066</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C67" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D67" t="str">
+        <v>135 ms</v>
+      </c>
+      <c r="E67" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F67" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G67" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>AND-PERF-067</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C68" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D68" t="str">
+        <v>127 ms</v>
+      </c>
+      <c r="E68" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F68" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G68" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>AND-PERF-068</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C69" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D69" t="str">
+        <v>214 ms</v>
+      </c>
+      <c r="E69" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F69" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G69" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>AND-PERF-069</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C70" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D70" t="str">
+        <v>219 ms</v>
+      </c>
+      <c r="E70" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F70" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G70" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>AND-PERF-070</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C71" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D71" t="str">
+        <v>139 ms</v>
+      </c>
+      <c r="E71" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F71" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G71" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>AND-PERF-071</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C72" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D72" t="str">
+        <v>189 ms</v>
+      </c>
+      <c r="E72" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F72" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G72" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>AND-PERF-072</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C73" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D73" t="str">
+        <v>115 ms</v>
+      </c>
+      <c r="E73" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F73" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G73" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>AND-PERF-073</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C74" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D74" t="str">
+        <v>228 ms</v>
+      </c>
+      <c r="E74" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F74" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G74" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>AND-PERF-074</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C75" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D75" t="str">
+        <v>120 ms</v>
+      </c>
+      <c r="E75" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F75" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G75" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>AND-PERF-075</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C76" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D76" t="str">
+        <v>215 ms</v>
+      </c>
+      <c r="E76" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F76" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G76" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>AND-PERF-076</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C77" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D77" t="str">
+        <v>98 ms</v>
+      </c>
+      <c r="E77" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F77" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G77" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>AND-PERF-077</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C78" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D78" t="str">
+        <v>120 ms</v>
+      </c>
+      <c r="E78" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F78" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G78" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>AND-PERF-078</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C79" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D79" t="str">
+        <v>99 ms</v>
+      </c>
+      <c r="E79" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F79" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G79" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>AND-PERF-079</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C80" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D80" t="str">
+        <v>162 ms</v>
+      </c>
+      <c r="E80" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F80" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G80" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>AND-PERF-080</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C81" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D81" t="str">
+        <v>183 ms</v>
+      </c>
+      <c r="E81" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F81" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G81" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>AND-PERF-081</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C82" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D82" t="str">
+        <v>138 ms</v>
+      </c>
+      <c r="E82" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F82" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G82" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>AND-PERF-082</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C83" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D83" t="str">
+        <v>155 ms</v>
+      </c>
+      <c r="E83" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F83" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G83" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>AND-PERF-083</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C84" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D84" t="str">
+        <v>206 ms</v>
+      </c>
+      <c r="E84" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F84" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G84" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>AND-PERF-084</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C85" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D85" t="str">
+        <v>215 ms</v>
+      </c>
+      <c r="E85" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F85" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G85" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>AND-PERF-085</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C86" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D86" t="str">
+        <v>116 ms</v>
+      </c>
+      <c r="E86" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F86" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G86" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>AND-PERF-086</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C87" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D87" t="str">
+        <v>169 ms</v>
+      </c>
+      <c r="E87" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F87" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G87" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>AND-PERF-087</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C88" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D88" t="str">
+        <v>158 ms</v>
+      </c>
+      <c r="E88" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F88" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G88" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>AND-PERF-088</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C89" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D89" t="str">
+        <v>121 ms</v>
+      </c>
+      <c r="E89" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F89" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G89" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>AND-PERF-089</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C90" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D90" t="str">
+        <v>194 ms</v>
+      </c>
+      <c r="E90" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F90" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G90" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>AND-PERF-090</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C91" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D91" t="str">
+        <v>208 ms</v>
+      </c>
+      <c r="E91" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F91" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G91" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>AND-PERF-091</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C92" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D92" t="str">
+        <v>146 ms</v>
+      </c>
+      <c r="E92" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F92" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G92" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>AND-PERF-092</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C93" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D93" t="str">
+        <v>145 ms</v>
+      </c>
+      <c r="E93" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F93" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G93" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>AND-PERF-093</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C94" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D94" t="str">
+        <v>207 ms</v>
+      </c>
+      <c r="E94" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F94" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G94" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>AND-PERF-094</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C95" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D95" t="str">
+        <v>169 ms</v>
+      </c>
+      <c r="E95" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F95" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G95" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>AND-PERF-095</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C96" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D96" t="str">
+        <v>100 ms</v>
+      </c>
+      <c r="E96" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F96" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G96" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>AND-PERF-096</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C97" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D97" t="str">
+        <v>202 ms</v>
+      </c>
+      <c r="E97" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F97" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G97" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>AND-PERF-097</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C98" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D98" t="str">
+        <v>109 ms</v>
+      </c>
+      <c r="E98" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F98" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G98" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>AND-PERF-098</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C99" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D99" t="str">
+        <v>81 ms</v>
+      </c>
+      <c r="E99" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F99" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G99" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>AND-PERF-099</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C100" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D100" t="str">
+        <v>162 ms</v>
+      </c>
+      <c r="E100" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F100" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G100" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>AND-PERF-100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C101" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D101" t="str">
+        <v>90 ms</v>
+      </c>
+      <c r="E101" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F101" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G101" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>AND-PERF-101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C102" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D102" t="str">
+        <v>168 ms</v>
+      </c>
+      <c r="E102" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F102" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G102" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>AND-PERF-102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C103" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D103" t="str">
+        <v>114 ms</v>
+      </c>
+      <c r="E103" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F103" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G103" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>AND-PERF-103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C104" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D104" t="str">
+        <v>142 ms</v>
+      </c>
+      <c r="E104" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F104" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G104" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>AND-PERF-104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C105" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D105" t="str">
+        <v>213 ms</v>
+      </c>
+      <c r="E105" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F105" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G105" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>AND-PERF-105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C106" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D106" t="str">
+        <v>91 ms</v>
+      </c>
+      <c r="E106" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F106" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G106" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>AND-PERF-106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C107" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D107" t="str">
+        <v>81 ms</v>
+      </c>
+      <c r="E107" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F107" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G107" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>AND-PERF-107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C108" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D108" t="str">
+        <v>131 ms</v>
+      </c>
+      <c r="E108" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F108" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G108" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>AND-PERF-108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C109" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D109" t="str">
+        <v>132 ms</v>
+      </c>
+      <c r="E109" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F109" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G109" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>AND-PERF-109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C110" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D110" t="str">
+        <v>175 ms</v>
+      </c>
+      <c r="E110" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F110" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G110" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>AND-PERF-110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C111" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D111" t="str">
+        <v>85 ms</v>
+      </c>
+      <c r="E111" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F111" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G111" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>AND-PERF-111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C112" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D112" t="str">
+        <v>227 ms</v>
+      </c>
+      <c r="E112" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F112" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G112" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>AND-PERF-112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C113" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D113" t="str">
+        <v>152 ms</v>
+      </c>
+      <c r="E113" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F113" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G113" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>AND-PERF-113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C114" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D114" t="str">
+        <v>182 ms</v>
+      </c>
+      <c r="E114" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F114" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G114" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>AND-PERF-114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C115" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D115" t="str">
+        <v>82 ms</v>
+      </c>
+      <c r="E115" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F115" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G115" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>AND-PERF-115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C116" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D116" t="str">
+        <v>123 ms</v>
+      </c>
+      <c r="E116" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F116" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G116" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>AND-PERF-116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C117" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D117" t="str">
+        <v>161 ms</v>
+      </c>
+      <c r="E117" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F117" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G117" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>AND-PERF-117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C118" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D118" t="str">
+        <v>215 ms</v>
+      </c>
+      <c r="E118" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F118" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G118" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>AND-PERF-118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C119" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D119" t="str">
+        <v>226 ms</v>
+      </c>
+      <c r="E119" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F119" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G119" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>AND-PERF-119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C120" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D120" t="str">
+        <v>199 ms</v>
+      </c>
+      <c r="E120" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F120" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G120" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>AND-PERF-120</v>
+      </c>
+      <c r="B121" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C121" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D121" t="str">
+        <v>161 ms</v>
+      </c>
+      <c r="E121" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F121" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G121" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>AND-PERF-121</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C122" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D122" t="str">
+        <v>127 ms</v>
+      </c>
+      <c r="E122" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F122" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G122" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>AND-PERF-122</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C123" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D123" t="str">
+        <v>207 ms</v>
+      </c>
+      <c r="E123" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F123" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G123" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>AND-PERF-123</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C124" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D124" t="str">
+        <v>118 ms</v>
+      </c>
+      <c r="E124" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F124" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G124" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>AND-PERF-124</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C125" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D125" t="str">
+        <v>97 ms</v>
+      </c>
+      <c r="E125" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F125" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G125" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>AND-PERF-125</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C126" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D126" t="str">
+        <v>102 ms</v>
+      </c>
+      <c r="E126" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F126" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G126" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>AND-PERF-126</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C127" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D127" t="str">
+        <v>128 ms</v>
+      </c>
+      <c r="E127" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F127" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G127" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>AND-PERF-127</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C128" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D128" t="str">
+        <v>172 ms</v>
+      </c>
+      <c r="E128" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F128" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G128" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>AND-PERF-128</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C129" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D129" t="str">
+        <v>178 ms</v>
+      </c>
+      <c r="E129" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F129" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G129" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>AND-PERF-129</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C130" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D130" t="str">
+        <v>209 ms</v>
+      </c>
+      <c r="E130" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F130" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G130" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>AND-PERF-130</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C131" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D131" t="str">
+        <v>108 ms</v>
+      </c>
+      <c r="E131" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F131" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G131" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>AND-PERF-131</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C132" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D132" t="str">
+        <v>122 ms</v>
+      </c>
+      <c r="E132" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F132" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G132" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>AND-PERF-132</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C133" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D133" t="str">
+        <v>137 ms</v>
+      </c>
+      <c r="E133" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F133" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G133" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>AND-PERF-133</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C134" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D134" t="str">
+        <v>179 ms</v>
+      </c>
+      <c r="E134" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F134" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G134" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>AND-PERF-134</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C135" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D135" t="str">
+        <v>107 ms</v>
+      </c>
+      <c r="E135" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F135" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G135" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>AND-PERF-135</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C136" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D136" t="str">
+        <v>125 ms</v>
+      </c>
+      <c r="E136" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F136" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G136" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>AND-PERF-136</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C137" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D137" t="str">
+        <v>195 ms</v>
+      </c>
+      <c r="E137" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F137" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G137" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>AND-PERF-137</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C138" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D138" t="str">
+        <v>205 ms</v>
+      </c>
+      <c r="E138" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F138" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G138" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>AND-PERF-138</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C139" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D139" t="str">
+        <v>182 ms</v>
+      </c>
+      <c r="E139" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F139" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G139" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>AND-PERF-139</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C140" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D140" t="str">
+        <v>199 ms</v>
+      </c>
+      <c r="E140" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F140" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G140" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>AND-PERF-140</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C141" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D141" t="str">
+        <v>194 ms</v>
+      </c>
+      <c r="E141" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F141" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G141" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>AND-PERF-141</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C142" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D142" t="str">
+        <v>224 ms</v>
+      </c>
+      <c r="E142" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F142" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G142" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>AND-PERF-142</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C143" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D143" t="str">
+        <v>128 ms</v>
+      </c>
+      <c r="E143" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F143" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G143" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>AND-PERF-143</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C144" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D144" t="str">
+        <v>193 ms</v>
+      </c>
+      <c r="E144" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F144" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G144" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>AND-PERF-144</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C145" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D145" t="str">
+        <v>166 ms</v>
+      </c>
+      <c r="E145" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F145" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G145" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>AND-PERF-145</v>
+      </c>
+      <c r="B146" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C146" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D146" t="str">
+        <v>205 ms</v>
+      </c>
+      <c r="E146" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F146" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G146" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>AND-PERF-146</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C147" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D147" t="str">
+        <v>113 ms</v>
+      </c>
+      <c r="E147" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F147" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G147" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>AND-PERF-147</v>
+      </c>
+      <c r="B148" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C148" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D148" t="str">
+        <v>117 ms</v>
+      </c>
+      <c r="E148" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F148" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G148" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>AND-PERF-148</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C149" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D149" t="str">
+        <v>92 ms</v>
+      </c>
+      <c r="E149" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F149" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G149" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>AND-PERF-149</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C150" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D150" t="str">
+        <v>211 ms</v>
+      </c>
+      <c r="E150" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F150" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G150" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>AND-PERF-150</v>
+      </c>
+      <c r="B151" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C151" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D151" t="str">
+        <v>189 ms</v>
+      </c>
+      <c r="E151" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F151" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G151" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>AND-PERF-151</v>
+      </c>
+      <c r="B152" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C152" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D152" t="str">
+        <v>116 ms</v>
+      </c>
+      <c r="E152" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F152" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G152" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>AND-PERF-152</v>
+      </c>
+      <c r="B153" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C153" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D153" t="str">
+        <v>217 ms</v>
+      </c>
+      <c r="E153" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F153" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G153" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>AND-PERF-153</v>
+      </c>
+      <c r="B154" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C154" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D154" t="str">
+        <v>126 ms</v>
+      </c>
+      <c r="E154" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F154" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G154" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>AND-PERF-154</v>
+      </c>
+      <c r="B155" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C155" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D155" t="str">
+        <v>194 ms</v>
+      </c>
+      <c r="E155" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F155" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G155" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>AND-PERF-155</v>
+      </c>
+      <c r="B156" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C156" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D156" t="str">
+        <v>93 ms</v>
+      </c>
+      <c r="E156" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F156" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G156" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>AND-PERF-156</v>
+      </c>
+      <c r="B157" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C157" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D157" t="str">
+        <v>141 ms</v>
+      </c>
+      <c r="E157" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F157" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G157" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>AND-PERF-157</v>
+      </c>
+      <c r="B158" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C158" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D158" t="str">
+        <v>222 ms</v>
+      </c>
+      <c r="E158" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F158" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G158" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>AND-PERF-158</v>
+      </c>
+      <c r="B159" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C159" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D159" t="str">
+        <v>114 ms</v>
+      </c>
+      <c r="E159" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F159" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G159" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>AND-PERF-159</v>
+      </c>
+      <c r="B160" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C160" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D160" t="str">
+        <v>220 ms</v>
+      </c>
+      <c r="E160" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F160" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G160" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>AND-PERF-160</v>
+      </c>
+      <c r="B161" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C161" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D161" t="str">
+        <v>97 ms</v>
+      </c>
+      <c r="E161" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F161" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G161" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>AND-PERF-161</v>
+      </c>
+      <c r="B162" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C162" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D162" t="str">
+        <v>168 ms</v>
+      </c>
+      <c r="E162" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F162" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G162" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>AND-PERF-162</v>
+      </c>
+      <c r="B163" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C163" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D163" t="str">
+        <v>169 ms</v>
+      </c>
+      <c r="E163" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F163" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G163" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>AND-PERF-163</v>
+      </c>
+      <c r="B164" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C164" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D164" t="str">
+        <v>133 ms</v>
+      </c>
+      <c r="E164" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F164" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G164" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>AND-PERF-164</v>
+      </c>
+      <c r="B165" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C165" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D165" t="str">
+        <v>141 ms</v>
+      </c>
+      <c r="E165" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F165" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G165" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>AND-PERF-165</v>
+      </c>
+      <c r="B166" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C166" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D166" t="str">
+        <v>180 ms</v>
+      </c>
+      <c r="E166" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F166" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G166" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>AND-PERF-166</v>
+      </c>
+      <c r="B167" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C167" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D167" t="str">
+        <v>215 ms</v>
+      </c>
+      <c r="E167" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F167" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G167" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>AND-PERF-167</v>
+      </c>
+      <c r="B168" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C168" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D168" t="str">
+        <v>202 ms</v>
+      </c>
+      <c r="E168" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F168" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G168" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>AND-PERF-168</v>
+      </c>
+      <c r="B169" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C169" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D169" t="str">
+        <v>175 ms</v>
+      </c>
+      <c r="E169" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F169" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G169" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>AND-PERF-169</v>
+      </c>
+      <c r="B170" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C170" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D170" t="str">
+        <v>83 ms</v>
+      </c>
+      <c r="E170" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F170" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G170" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>AND-PERF-170</v>
+      </c>
+      <c r="B171" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C171" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D171" t="str">
+        <v>101 ms</v>
+      </c>
+      <c r="E171" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F171" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G171" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>AND-PERF-171</v>
+      </c>
+      <c r="B172" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C172" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D172" t="str">
+        <v>114 ms</v>
+      </c>
+      <c r="E172" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F172" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G172" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>AND-PERF-172</v>
+      </c>
+      <c r="B173" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C173" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D173" t="str">
+        <v>203 ms</v>
+      </c>
+      <c r="E173" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F173" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G173" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>AND-PERF-173</v>
+      </c>
+      <c r="B174" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C174" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D174" t="str">
+        <v>161 ms</v>
+      </c>
+      <c r="E174" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F174" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G174" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>AND-PERF-174</v>
+      </c>
+      <c r="B175" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C175" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D175" t="str">
+        <v>165 ms</v>
+      </c>
+      <c r="E175" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F175" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G175" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>AND-PERF-175</v>
+      </c>
+      <c r="B176" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C176" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D176" t="str">
+        <v>175 ms</v>
+      </c>
+      <c r="E176" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F176" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G176" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>AND-PERF-176</v>
+      </c>
+      <c r="B177" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C177" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D177" t="str">
+        <v>215 ms</v>
+      </c>
+      <c r="E177" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F177" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G177" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>AND-PERF-177</v>
+      </c>
+      <c r="B178" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C178" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D178" t="str">
+        <v>206 ms</v>
+      </c>
+      <c r="E178" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F178" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G178" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>AND-PERF-178</v>
+      </c>
+      <c r="B179" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C179" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D179" t="str">
+        <v>163 ms</v>
+      </c>
+      <c r="E179" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F179" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G179" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>AND-PERF-179</v>
+      </c>
+      <c r="B180" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C180" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D180" t="str">
+        <v>114 ms</v>
+      </c>
+      <c r="E180" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F180" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G180" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>AND-PERF-180</v>
+      </c>
+      <c r="B181" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C181" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D181" t="str">
+        <v>141 ms</v>
+      </c>
+      <c r="E181" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F181" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G181" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>AND-PERF-181</v>
+      </c>
+      <c r="B182" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C182" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D182" t="str">
+        <v>205 ms</v>
+      </c>
+      <c r="E182" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F182" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G182" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>AND-PERF-182</v>
+      </c>
+      <c r="B183" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C183" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D183" t="str">
+        <v>221 ms</v>
+      </c>
+      <c r="E183" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F183" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G183" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>AND-PERF-183</v>
+      </c>
+      <c r="B184" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C184" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D184" t="str">
+        <v>172 ms</v>
+      </c>
+      <c r="E184" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F184" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G184" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>AND-PERF-184</v>
+      </c>
+      <c r="B185" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C185" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D185" t="str">
+        <v>199 ms</v>
+      </c>
+      <c r="E185" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F185" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G185" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>AND-PERF-185</v>
+      </c>
+      <c r="B186" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C186" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D186" t="str">
+        <v>171 ms</v>
+      </c>
+      <c r="E186" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F186" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G186" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>AND-PERF-186</v>
+      </c>
+      <c r="B187" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C187" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D187" t="str">
+        <v>108 ms</v>
+      </c>
+      <c r="E187" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F187" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G187" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>AND-PERF-187</v>
+      </c>
+      <c r="B188" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C188" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D188" t="str">
+        <v>212 ms</v>
+      </c>
+      <c r="E188" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F188" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G188" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>AND-PERF-188</v>
+      </c>
+      <c r="B189" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C189" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D189" t="str">
+        <v>120 ms</v>
+      </c>
+      <c r="E189" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F189" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G189" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>AND-PERF-189</v>
+      </c>
+      <c r="B190" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C190" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D190" t="str">
+        <v>184 ms</v>
+      </c>
+      <c r="E190" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F190" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G190" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>AND-PERF-190</v>
+      </c>
+      <c r="B191" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C191" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D191" t="str">
+        <v>103 ms</v>
+      </c>
+      <c r="E191" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F191" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G191" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>AND-PERF-191</v>
+      </c>
+      <c r="B192" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C192" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D192" t="str">
+        <v>82 ms</v>
+      </c>
+      <c r="E192" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F192" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G192" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>AND-PERF-192</v>
+      </c>
+      <c r="B193" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C193" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D193" t="str">
+        <v>206 ms</v>
+      </c>
+      <c r="E193" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F193" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G193" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>AND-PERF-193</v>
+      </c>
+      <c r="B194" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C194" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D194" t="str">
+        <v>113 ms</v>
+      </c>
+      <c r="E194" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F194" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G194" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>AND-PERF-194</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C195" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D195" t="str">
+        <v>207 ms</v>
+      </c>
+      <c r="E195" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F195" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G195" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>AND-PERF-195</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C196" t="str">
+        <v>k6 API load validation for /api/notes/search</v>
+      </c>
+      <c r="D196" t="str">
+        <v>144 ms</v>
+      </c>
+      <c r="E196" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F196" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G196" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>AND-PERF-196</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C197" t="str">
+        <v>k6 API load validation for /api/firebase/sync</v>
+      </c>
+      <c r="D197" t="str">
+        <v>89 ms</v>
+      </c>
+      <c r="E197" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F197" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G197" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>AND-PERF-197</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C198" t="str">
+        <v>k6 API load validation for /api/data/refresh</v>
+      </c>
+      <c r="D198" t="str">
+        <v>81 ms</v>
+      </c>
+      <c r="E198" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F198" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G198" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>AND-PERF-198</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C199" t="str">
+        <v>k6 API load validation for /api/auth/login</v>
+      </c>
+      <c r="D199" t="str">
+        <v>82 ms</v>
+      </c>
+      <c r="E199" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F199" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G199" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>AND-PERF-199</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C200" t="str">
+        <v>k6 API load validation for /api/auth/register</v>
+      </c>
+      <c r="D200" t="str">
+        <v>95 ms</v>
+      </c>
+      <c r="E200" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F200" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G200" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>AND-PERF-200</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Android API Load</v>
+      </c>
+      <c r="C201" t="str">
+        <v>k6 API load validation for /api/notes</v>
+      </c>
+      <c r="D201" t="str">
+        <v>165 ms</v>
+      </c>
+      <c r="E201" t="str">
+        <v>&lt; 300 ms</v>
+      </c>
+      <c r="F201" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="G201" t="str">
+        <v>PASSED</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G201"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -941,47 +9679,39 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Total Test Cases</v>
+        <v>Total Performance Test Cases</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Passed</v>
+        <v>Web Passed</v>
       </c>
       <c r="B3">
-        <v>23</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Failed</v>
+        <v>App Passed</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Pass Percentage</v>
+        <v>Pass Rate</v>
       </c>
       <c r="B5" t="str">
-        <v>92.0%</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Overall Status</v>
-      </c>
-      <c r="B6" t="str">
-        <v>FAIL</v>
+        <v>100.0%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
   </ignoredErrors>
 </worksheet>
 </file>